--- a/data/trans_dic/P1401-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1401-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,18</t>
+          <t>0,31; 3,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,28</t>
+          <t>0,24; 2,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,85</t>
+          <t>1,12; 5,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,44</t>
+          <t>0,99; 4,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,43</t>
+          <t>0,58; 2,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,46</t>
+          <t>1,06; 3,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,5</t>
+          <t>0,66; 2,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,84</t>
+          <t>0,53; 1,83</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,86</t>
+          <t>0,2; 1,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,15</t>
+          <t>0,2; 1,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,82</t>
+          <t>0,86; 3,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,72</t>
+          <t>0,42; 2,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,07</t>
+          <t>0,21; 2,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,59</t>
+          <t>0,82; 2,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,97</t>
+          <t>0,41; 1,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,51</t>
+          <t>0,4; 1,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,69</t>
+          <t>1,12; 2,62</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,81</t>
+          <t>0,65; 4,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,45</t>
+          <t>0,6; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,69</t>
+          <t>1,02; 3,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,65</t>
+          <t>0,61; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,25</t>
+          <t>1,97; 7,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,95</t>
+          <t>1,62; 4,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,28</t>
+          <t>0,94; 3,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,3</t>
+          <t>1,59; 4,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,5</t>
+          <t>1,61; 3,51</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,14</t>
+          <t>0,25; 2,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,24</t>
+          <t>0,55; 3,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,67</t>
+          <t>0,9; 3,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,14</t>
+          <t>1,51; 5,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,26</t>
+          <t>1,53; 5,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,49</t>
+          <t>1,83; 4,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,25</t>
+          <t>1,08; 3,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,58</t>
+          <t>1,29; 3,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,05</t>
+          <t>1,71; 3,55</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 7,24</t>
+          <t>0,54; 6,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,78</t>
+          <t>0,42; 3,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,68</t>
+          <t>0,98; 4,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,05</t>
+          <t>0,44; 4,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,32</t>
+          <t>2,12; 5,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,26</t>
+          <t>0,91; 4,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,17</t>
+          <t>0,23; 2,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,37</t>
+          <t>1,93; 4,13</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,56</t>
+          <t>0,39; 3,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,75</t>
+          <t>1,66; 4,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,99</t>
+          <t>0,36; 3,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,76</t>
+          <t>1,23; 3,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,63</t>
+          <t>0,57; 2,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,72</t>
+          <t>1,7; 3,61</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,66</t>
+          <t>0,3; 1,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,55</t>
+          <t>0,27; 1,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,03</t>
+          <t>1,57; 3,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,36</t>
+          <t>1,69; 4,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,76</t>
+          <t>1,32; 3,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,17</t>
+          <t>0,97; 2,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,57</t>
+          <t>1,16; 2,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,48</t>
+          <t>0,92; 2,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,69</t>
+          <t>1,51; 2,81</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,82</t>
+          <t>0,4; 1,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,85</t>
+          <t>0,23; 1,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,57</t>
+          <t>1,27; 3,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,67</t>
+          <t>0,88; 2,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,39</t>
+          <t>1,22; 3,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,25</t>
+          <t>2,17; 4,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,92</t>
+          <t>0,85; 2,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,18</t>
+          <t>0,93; 2,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,02</t>
+          <t>2,0; 3,39</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,55</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,22</t>
+          <t>0,62; 1,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,48</t>
+          <t>1,65; 2,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,64</t>
+          <t>1,54; 2,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,67</t>
+          <t>1,51; 2,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,55</t>
+          <t>1,91; 2,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,94</t>
+          <t>1,31; 1,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,76</t>
+          <t>1,2; 1,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,4</t>
+          <t>1,94; 2,5</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6888</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>945; 9387</t>
+          <t>907; 8851</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4678</t>
+          <t>0; 5356</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>741; 7106</t>
+          <t>771; 7238</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3927; 16807</t>
+          <t>3220; 16226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2950; 12814</t>
+          <t>2871; 13167</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1556; 7036</t>
+          <t>1827; 7454</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6034; 20122</t>
+          <t>6180; 20164</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3681; 14590</t>
+          <t>3853; 14937</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2886; 11087</t>
+          <t>3371; 11638</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>18453</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>991; 9420</t>
+          <t>989; 8917</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1031; 10808</t>
+          <t>1030; 9457</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4692; 19746</t>
+          <t>4571; 19235</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2220; 14230</t>
+          <t>2214; 14564</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1148; 10835</t>
+          <t>1074; 11220</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3920; 13305</t>
+          <t>4458; 13762</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4956; 20292</t>
+          <t>4263; 19337</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4059; 15474</t>
+          <t>4122; 16203</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11495; 27688</t>
+          <t>12068; 28144</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>16022</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2101; 15577</t>
+          <t>2096; 15550</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1924; 10998</t>
+          <t>1927; 11117</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3498; 11674</t>
+          <t>3212; 11210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2123; 12439</t>
+          <t>2076; 12657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6256; 24399</t>
+          <t>6622; 23924</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5480; 13798</t>
+          <t>5773; 14876</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6343; 21787</t>
+          <t>6242; 22658</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10199; 28130</t>
+          <t>10417; 30274</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10668; 23251</t>
+          <t>10811; 23591</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>19532</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>953; 8013</t>
+          <t>933; 7922</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2030; 11990</t>
+          <t>2050; 11698</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2577; 11474</t>
+          <t>3359; 14096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5705; 20004</t>
+          <t>5871; 20412</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5168; 20353</t>
+          <t>5926; 20619</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5766; 16583</t>
+          <t>7723; 17631</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8068; 24809</t>
+          <t>8214; 24183</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9980; 27122</t>
+          <t>9764; 27854</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10440; 24006</t>
+          <t>13623; 28204</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>12330</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1172; 15389</t>
+          <t>1156; 14399</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>928; 7985</t>
+          <t>884; 7985</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2155; 8369</t>
+          <t>2023; 8944</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>970; 11095</t>
+          <t>960; 10601</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5671</t>
+          <t>0; 4985</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4618; 11062</t>
+          <t>4791; 11687</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4003; 18399</t>
+          <t>3914; 19532</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>983; 9337</t>
+          <t>986; 9519</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7861; 16901</t>
+          <t>8356; 17845</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13509</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1065; 9759</t>
+          <t>1066; 10383</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4809</t>
+          <t>0; 3212</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4414; 12809</t>
+          <t>4485; 12555</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>999; 8313</t>
+          <t>1005; 8394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6031</t>
+          <t>0; 6574</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3192; 9628</t>
+          <t>3224; 9902</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3155; 14523</t>
+          <t>3147; 14630</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 7027</t>
+          <t>0; 8323</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9076; 19587</t>
+          <t>9092; 19263</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>12292</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>27355</t>
+          <t>30750</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1892; 11032</t>
+          <t>1961; 12025</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1779; 10196</t>
+          <t>1788; 9549</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9948; 24994</t>
+          <t>11239; 28394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11217; 30225</t>
+          <t>11726; 30659</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8733; 25991</t>
+          <t>9148; 26131</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4633; 18390</t>
+          <t>7484; 18582</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15155; 34808</t>
+          <t>15795; 36644</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13188; 33476</t>
+          <t>12361; 31190</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16874; 39408</t>
+          <t>22425; 41611</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>41842</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3130; 14195</t>
+          <t>3152; 14999</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1916; 14393</t>
+          <t>1825; 12600</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5384; 23856</t>
+          <t>10128; 24890</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7487; 21996</t>
+          <t>7256; 22897</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9929; 28034</t>
+          <t>10102; 27828</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15725; 30426</t>
+          <t>18017; 34216</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12999; 30719</t>
+          <t>13615; 32910</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15327; 34968</t>
+          <t>14856; 34796</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>22337; 49645</t>
+          <t>32508; 55201</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>146817</t>
+          <t>159325</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>27339; 53228</t>
+          <t>28645; 54935</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20040; 41430</t>
+          <t>21201; 42386</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52962; 85695</t>
+          <t>58261; 90426</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56327; 93964</t>
+          <t>54850; 88816</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>55106; 94528</t>
+          <t>53433; 90386</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>60692; 93196</t>
+          <t>71138; 98188</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89974; 135408</t>
+          <t>91287; 134369</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>82250; 122264</t>
+          <t>82952; 123352</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>123640; 170753</t>
+          <t>140385; 181701</t>
         </is>
       </c>
     </row>
